--- a/sampleprojects/CorporateTax/excel/states/GA_corp.xlsx
+++ b/sampleprojects/CorporateTax/excel/states/GA_corp.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="78">
   <si>
     <t>DT: Determine GA Filing Requirement</t>
   </si>
@@ -148,7 +148,7 @@
     <t>Calculate GA tax at 5.75% flat rate; Georgia state corporate income tax calculation: Apply 5.75% flat rate, subtract credits, calculate refund or amount owed.</t>
   </si>
   <si>
-    <t>set apportionment.state_tax = apportionment.state_taxable_income * apportionment.state_tax_rate; set apportionment.state_tax = the maximum of (apportionment.state_tax - apportionment.state_credits) and (0.0); set apportionment.state_refund_or_owed = apportionment.state_payments - apportionment.state_tax; add ((((((("GA tax calculation: Taxable income: $" + string value of (apportionment.state_taxable_income)) + " x 5.75% = $") + string value of (apportionment.state_tax)) + ". Credits: $") + string value of (apportionment.state_credits)) + ". Final tax: $") + string value of (apportionment.state_tax)) + ". Reference: GA Form 600, GA Code § 48-7-21" to job.audit_trail;</t>
+    <t>set apportionment.state_tax = apportionment.state_taxable_income * ga_apportionment.state_tax_rate; set apportionment.state_tax = the maximum of (apportionment.state_tax - apportionment.state_credits) and (0.0); set apportionment.state_refund_or_owed = apportionment.state_payments - apportionment.state_tax; add ((((((("GA tax calculation: Taxable income: $" + string value of (apportionment.state_taxable_income)) + " x 5.75% = $") + string value of (apportionment.state_tax)) + ". Credits: $") + string value of (apportionment.state_credits)) + ". Final tax: $") + string value of (apportionment.state_tax)) + ". Reference: GA Form 600, GA Code § 48-7-21" to job.audit_trail;</t>
   </si>
   <si>
     <t>No nexus - no tax liability</t>
@@ -199,10 +199,10 @@
     <t>Reference</t>
   </si>
   <si>
-    <t>apportionment</t>
-  </si>
-  <si>
-    <t>(8 attributes)</t>
+    <t>ga_apportionment</t>
+  </si>
+  <si>
+    <t>(4 attributes)</t>
   </si>
   <si>
     <t>apportionment_formula</t>
@@ -230,36 +230,6 @@
   </si>
   <si>
     <t>GA economic nexus gross receipts threshold: $100,000</t>
-  </si>
-  <si>
-    <t>state_additions</t>
-  </si>
-  <si>
-    <t>0.0</t>
-  </si>
-  <si>
-    <t>GA-specific additions: federal interest, state addbacks</t>
-  </si>
-  <si>
-    <t>state_code</t>
-  </si>
-  <si>
-    <t>GA</t>
-  </si>
-  <si>
-    <t>Georgia state code</t>
-  </si>
-  <si>
-    <t>state_credits</t>
-  </si>
-  <si>
-    <t>GA tax credits: jobs credits, R&amp;D credits, film credits, etc.</t>
-  </si>
-  <si>
-    <t>state_subtractions</t>
-  </si>
-  <si>
-    <t>GA-specific subtractions: municipal interest, state deductions</t>
   </si>
   <si>
     <t>state_tax_rate</t>
@@ -2548,14 +2518,14 @@
       <c r="B7" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="C7" s="10" t="s">
-        <v>63</v>
+      <c r="C7" s="11" t="s">
+        <v>75</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>14</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>14</v>
@@ -2564,7 +2534,7 @@
         <v>65</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I7" s="8" t="s">
         <v>14</v>
@@ -2579,170 +2549,6 @@
         <v>14</v>
       </c>
       <c r="M7" s="8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="H8" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="L8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="M8" s="7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="H9" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="J9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="L9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="M9" s="8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="H10" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="L10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="M10" s="7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="H11" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="I11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="J11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="L11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="M11" s="8" t="s">
         <v>14</v>
       </c>
     </row>
